--- a/Problem6_Dynamic_Behavioral_Credit_Scoring/reports/financial_impact_reporting_packaging/AMEX_Problem6_Financial_Impact_Workbook.xlsx
+++ b/Problem6_Dynamic_Behavioral_Credit_Scoring/reports/financial_impact_reporting_packaging/AMEX_Problem6_Financial_Impact_Workbook.xlsx
@@ -20,10 +20,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-    <numFmt numFmtId="165" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="164" formatCode="$#,##0;($#,##0);-"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -74,6 +74,12 @@
       <name val="Calibri"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <i val="1"/>
+      <color rgb="000B1F3A"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="8">
@@ -126,7 +132,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -137,7 +143,7 @@
     <xf numFmtId="3" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -151,14 +157,22 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="6" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="164" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -682,7 +696,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F14"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="2" max="2"/>
@@ -692,6 +706,7 @@
     <col width="3" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -703,6 +718,13 @@
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>Financial Impact Summary</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>Project Portfolio Prepared By Nandagopal R</t>
         </is>
       </c>
     </row>
@@ -735,7 +757,7 @@
           <t>Net Benefit / Cycle</t>
         </is>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="18">
         <f>'Recency Impact'!B11</f>
         <v/>
       </c>
@@ -848,7 +870,7 @@
           <t>Ead Per Account Usd</t>
         </is>
       </c>
-      <c r="B2" s="12" t="n">
+      <c r="B2" s="19" t="n">
         <v>5000</v>
       </c>
       <c r="C2" s="13" t="inlineStr">
@@ -863,7 +885,7 @@
           <t>Lgd Assumption</t>
         </is>
       </c>
-      <c r="B3" s="14" t="n">
+      <c r="B3" s="20" t="n">
         <v>0.45</v>
       </c>
       <c r="C3" s="13" t="inlineStr">
@@ -878,7 +900,7 @@
           <t>Behavioral Intervention Success Rate</t>
         </is>
       </c>
-      <c r="B4" s="14" t="n">
+      <c r="B4" s="20" t="n">
         <v>0.2</v>
       </c>
       <c r="C4" s="13" t="inlineStr">
@@ -893,7 +915,7 @@
           <t>False Positive Review Cost Usd</t>
         </is>
       </c>
-      <c r="B5" s="12" t="n">
+      <c r="B5" s="19" t="n">
         <v>35</v>
       </c>
       <c r="C5" s="13" t="inlineStr">
@@ -908,7 +930,7 @@
           <t>Implementation Cost Usd</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="19" t="n">
         <v>60000</v>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -1021,7 +1043,7 @@
           <t>Real Defaulter Capture Rate</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="21" t="n">
         <v>0.8384788830110138</v>
       </c>
     </row>
@@ -1042,7 +1064,7 @@
           <t>Gross Loss Prevented / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B9" s="17">
+      <c r="B9" s="22">
         <f>B8*Assumptions!$B$2*Assumptions!$B$3</f>
         <v/>
       </c>
@@ -1053,7 +1075,7 @@
           <t>False-Positive Review Cost / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B10" s="17">
+      <c r="B10" s="22">
         <f>B6*Assumptions!$B$5</f>
         <v/>
       </c>
@@ -1064,7 +1086,7 @@
           <t>Net Benefit / Cycle (USD)</t>
         </is>
       </c>
-      <c r="B11" s="17">
+      <c r="B11" s="22">
         <f>B9-B10</f>
         <v/>
       </c>
@@ -1075,7 +1097,7 @@
           <t>Annual Net Benefit (USD)</t>
         </is>
       </c>
-      <c r="B12" s="17">
+      <c r="B12" s="22">
         <f>B11*Assumptions!$B$7</f>
         <v/>
       </c>
